--- a/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Ra8890f880ed244ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R2cce1379e9104081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R934572c9f4c74dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R5b1805371c124033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Rc67b05da01b8422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rc0a260630ae54dc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43372,7 +43372,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-12 01:02:51+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 07:02:47+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
